--- a/XProject/Assets/ExtraRes/Configs/Excel/MergeableItem.xlsx
+++ b/XProject/Assets/ExtraRes/Configs/Excel/MergeableItem.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +27,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="66">
+  <si>
+    <t>#</t>
+  </si>
   <si>
     <t>id</t>
   </si>
@@ -146,7 +147,75 @@
   </si>
   <si>
     <r>
-      <t>1景观|2人物|3动物|4精灵果|</t>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>景观</t>
+    </r>
+  </si>
+  <si>
+    <t>初始是否解锁</t>
+  </si>
+  <si>
+    <t>物品所占三合地块大小</t>
+  </si>
+  <si>
+    <t>合成链id</t>
+  </si>
+  <si>
+    <t>产出权重</t>
+  </si>
+  <si>
+    <t>预制体</t>
+  </si>
+  <si>
+    <t>图标</t>
+  </si>
+  <si>
+    <t>spine资源</t>
+  </si>
+  <si>
+    <t>等级</t>
+  </si>
+  <si>
+    <t>出售价格(装修币)</t>
+  </si>
+  <si>
+    <t>购买价格(装修币)</t>
+  </si>
+  <si>
+    <t>计费点id</t>
+  </si>
+  <si>
+    <t>气球价格(装修币)</t>
+  </si>
+  <si>
+    <t>气球价格(关联商品)</t>
+  </si>
+  <si>
+    <t>是否能与万能牌进行合成</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>使用方式（</t>
     </r>
     <r>
       <rPr>
@@ -155,8 +224,16 @@
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">
-</t>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>无法使用，</t>
     </r>
     <r>
       <rPr>
@@ -165,7 +242,16 @@
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
-      <t>5礼盒|6装修币箱|7体力宝箱|</t>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>点击使用，</t>
     </r>
     <r>
       <rPr>
@@ -174,82 +260,17 @@
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">
-</t>
+      <t>2</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>8金币宝箱|9城堡升级装修币|10万能牌|</t>
+      <t>自动使用）</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>11元素宝箱|12上锁宝箱</t>
-    </r>
-  </si>
-  <si>
-    <t>初始是否解锁</t>
-  </si>
-  <si>
-    <t>物品所占三合地块大小</t>
-  </si>
-  <si>
-    <t>合成链id</t>
-  </si>
-  <si>
-    <t>产出权重</t>
-  </si>
-  <si>
-    <t>预制体</t>
-  </si>
-  <si>
-    <t>图标</t>
-  </si>
-  <si>
-    <t>spine资源</t>
-  </si>
-  <si>
-    <t>等级</t>
-  </si>
-  <si>
-    <t>出售价格(装修币)</t>
-  </si>
-  <si>
-    <t>购买价格(装修币)</t>
-  </si>
-  <si>
-    <t>计费点id</t>
-  </si>
-  <si>
-    <t>气球价格(装修币)</t>
-  </si>
-  <si>
-    <t>气球价格(关联商品)</t>
-  </si>
-  <si>
-    <t>是否能与万能牌进行合成</t>
-  </si>
-  <si>
-    <t>使用方式（0无法使用，1点击使用，2自动使用）</t>
   </si>
   <si>
     <t>产出物品（物品id，数量）</t>
@@ -295,7 +316,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -307,6 +328,12 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -873,137 +900,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1022,22 +1049,25 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1354,14 +1384,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AB4"/>
+  <dimension ref="A1:AC4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3"/>
   <sheetData>
-    <row r="1" ht="55.95" spans="1:28">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="55.95" spans="1:29">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -1442,98 +1472,104 @@
       <c r="AB1" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="AC1" s="2" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" ht="28.35" spans="1:28">
-      <c r="A2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>1</v>
+    <row r="2" ht="28.35" spans="1:29">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>30</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>31</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="L2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="P2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="N2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>28</v>
-      </c>
       <c r="Q2" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="U2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="W2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="X2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y2" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA2" s="4" t="s">
+      <c r="AC2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="AB2" s="4" t="s">
-        <v>28</v>
-      </c>
     </row>
-    <row r="3" ht="72" customHeight="1" spans="1:28">
-      <c r="A3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" s="4" t="s">
+    <row r="3" ht="72" customHeight="1" spans="1:29">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C3" s="4" t="s">
@@ -1545,13 +1581,13 @@
       <c r="E3" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="6" t="s">
         <v>40</v>
       </c>
       <c r="I3" s="4" t="s">
@@ -1593,7 +1629,7 @@
       <c r="U3" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="V3" s="4" t="s">
+      <c r="V3" s="6" t="s">
         <v>54</v>
       </c>
       <c r="W3" s="4" t="s">
@@ -1614,100 +1650,79 @@
       <c r="AB3" s="4" t="s">
         <v>60</v>
       </c>
+      <c r="AC3" s="4" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="4" ht="25" customHeight="1" spans="1:28">
-      <c r="A4" s="6">
+    <row r="4" ht="25" customHeight="1" spans="2:29">
+      <c r="B4" s="7">
         <v>399999</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" s="7">
+      <c r="C4" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="8">
         <v>101</v>
       </c>
-      <c r="D4" s="7">
+      <c r="E4" s="8">
         <v>101</v>
       </c>
-      <c r="E4" s="7">
+      <c r="F4" s="8">
         <v>1</v>
       </c>
-      <c r="F4" s="7">
+      <c r="G4" s="8">
         <v>11</v>
       </c>
-      <c r="G4" s="7" t="b">
+      <c r="H4" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="H4" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="I4" s="9"/>
+      <c r="I4" s="8" t="s">
+        <v>63</v>
+      </c>
       <c r="J4" s="10"/>
-      <c r="K4" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="L4" s="7" t="s">
+      <c r="K4" s="11"/>
+      <c r="L4" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="M4" s="10"/>
-      <c r="N4" s="7">
+      <c r="M4" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="N4" s="11"/>
+      <c r="O4" s="8">
         <v>1</v>
       </c>
-      <c r="O4" s="7">
+      <c r="P4" s="8">
         <v>0</v>
       </c>
-      <c r="P4" s="7">
+      <c r="Q4" s="8">
         <v>0</v>
       </c>
-      <c r="Q4" s="10"/>
-      <c r="R4" s="7">
+      <c r="R4" s="11"/>
+      <c r="S4" s="8">
         <v>0</v>
       </c>
-      <c r="S4" s="10"/>
-      <c r="T4" s="7" t="b">
+      <c r="T4" s="11"/>
+      <c r="U4" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="U4" s="7">
+      <c r="V4" s="8">
         <v>1</v>
       </c>
-      <c r="V4" s="11"/>
-      <c r="W4" s="10"/>
-      <c r="X4" s="7">
+      <c r="W4" s="12"/>
+      <c r="X4" s="11"/>
+      <c r="Y4" s="8">
         <v>2</v>
       </c>
-      <c r="Y4" s="10"/>
-      <c r="Z4" s="12" t="b">
+      <c r="Z4" s="11"/>
+      <c r="AA4" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="AA4" s="10"/>
-      <c r="AB4" s="10"/>
+      <c r="AB4" s="11"/>
+      <c r="AC4" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/XProject/Assets/ExtraRes/Configs/Excel/MergeableItem.xlsx
+++ b/XProject/Assets/ExtraRes/Configs/Excel/MergeableItem.xlsx
@@ -27,10 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="66">
-  <si>
-    <t>#</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="65">
   <si>
     <t>id</t>
   </si>
@@ -1384,14 +1381,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AB4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3"/>
   <sheetData>
-    <row r="1" ht="55.95" spans="1:29">
-      <c r="A1" t="s">
+    <row r="1" ht="55.95" spans="1:28">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -1472,104 +1469,98 @@
       <c r="AB1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="2" t="s">
+    </row>
+    <row r="2" ht="28.35" spans="1:28">
+      <c r="A2" s="3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" ht="28.35" spans="1:29">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>2</v>
-      </c>
       <c r="D2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>30</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>29</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>31</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="T2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="M2" s="9" t="s">
+      <c r="U2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="N2" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="O2" s="4" t="s">
+      <c r="AA2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="P2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="W2" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="X2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="Z2" s="4" t="s">
+      <c r="AB2" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" ht="72" customHeight="1" spans="1:28">
+      <c r="A3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="AA2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AB2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="AC2" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" ht="72" customHeight="1" spans="1:29">
-      <c r="A3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C3" s="4" t="s">
@@ -1581,13 +1572,13 @@
       <c r="E3" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="4" t="s">
         <v>40</v>
       </c>
       <c r="I3" s="4" t="s">
@@ -1626,10 +1617,10 @@
       <c r="T3" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="U3" s="4" t="s">
+      <c r="U3" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="V3" s="6" t="s">
+      <c r="V3" s="4" t="s">
         <v>54</v>
       </c>
       <c r="W3" s="4" t="s">
@@ -1650,75 +1641,72 @@
       <c r="AB3" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AC3" s="4" t="s">
+    </row>
+    <row r="4" ht="25" customHeight="1" spans="1:28">
+      <c r="A4" s="7">
+        <v>399999</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="4" ht="25" customHeight="1" spans="2:29">
-      <c r="B4" s="7">
-        <v>399999</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>62</v>
+      <c r="C4" s="8">
+        <v>101</v>
       </c>
       <c r="D4" s="8">
         <v>101</v>
       </c>
       <c r="E4" s="8">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="F4" s="8">
-        <v>1</v>
-      </c>
-      <c r="G4" s="8">
         <v>11</v>
       </c>
-      <c r="H4" s="8" t="b">
+      <c r="G4" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="H4" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I4" s="10"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="J4" s="10"/>
-      <c r="K4" s="11"/>
       <c r="L4" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="M4" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="N4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="8">
+        <v>1</v>
+      </c>
       <c r="O4" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" s="8">
         <v>0</v>
       </c>
-      <c r="Q4" s="8">
+      <c r="Q4" s="11"/>
+      <c r="R4" s="8">
         <v>0</v>
       </c>
-      <c r="R4" s="11"/>
-      <c r="S4" s="8">
+      <c r="S4" s="11"/>
+      <c r="T4" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="T4" s="11"/>
-      <c r="U4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" s="8">
+      <c r="U4" s="8">
         <v>1</v>
       </c>
-      <c r="W4" s="12"/>
-      <c r="X4" s="11"/>
-      <c r="Y4" s="8">
+      <c r="V4" s="12"/>
+      <c r="W4" s="11"/>
+      <c r="X4" s="8">
         <v>2</v>
       </c>
-      <c r="Z4" s="11"/>
-      <c r="AA4" s="13" t="b">
+      <c r="Y4" s="11"/>
+      <c r="Z4" s="13" t="b">
         <v>1</v>
       </c>
+      <c r="AA4" s="11"/>
       <c r="AB4" s="11"/>
-      <c r="AC4" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/XProject/Assets/ExtraRes/Configs/Excel/MergeableItem.xlsx
+++ b/XProject/Assets/ExtraRes/Configs/Excel/MergeableItem.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="104">
   <si>
     <t>id</t>
   </si>
@@ -144,12 +144,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
       <t>1</t>
     </r>
     <r>
@@ -159,7 +153,43 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>景观</t>
+      <t>宝箱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>合成物</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>万能牌</t>
     </r>
   </si>
   <si>
@@ -301,6 +331,123 @@
   </si>
   <si>
     <t>test_three_merge_box</t>
+  </si>
+  <si>
+    <t>花圃1</t>
+  </si>
+  <si>
+    <t>Merge3_build_011</t>
+  </si>
+  <si>
+    <t>Merge3_build_011_desc</t>
+  </si>
+  <si>
+    <t>ThreeMergeableItem</t>
+  </si>
+  <si>
+    <t>ui_map1_icon_magicTree_1</t>
+  </si>
+  <si>
+    <t>花圃2</t>
+  </si>
+  <si>
+    <t>Merge3_build_012</t>
+  </si>
+  <si>
+    <t>Merge3_build_012_desc</t>
+  </si>
+  <si>
+    <t>ui_map1_icon_magicTree_2</t>
+  </si>
+  <si>
+    <t>花圃3</t>
+  </si>
+  <si>
+    <t>Merge3_build_013</t>
+  </si>
+  <si>
+    <t>Merge3_build_013_desc</t>
+  </si>
+  <si>
+    <t>ui_map1_icon_magicTree_3</t>
+  </si>
+  <si>
+    <t>花圃4</t>
+  </si>
+  <si>
+    <t>Merge3_build_014</t>
+  </si>
+  <si>
+    <t>Merge3_build_014_desc</t>
+  </si>
+  <si>
+    <t>ui_map1_icon_magicTree_4</t>
+  </si>
+  <si>
+    <t>花圃5</t>
+  </si>
+  <si>
+    <t>Merge3_build_015</t>
+  </si>
+  <si>
+    <t>Merge3_build_015_desc</t>
+  </si>
+  <si>
+    <t>ui_map1_icon_magicTree_5</t>
+  </si>
+  <si>
+    <t>花圃6</t>
+  </si>
+  <si>
+    <t>Merge3_build_016</t>
+  </si>
+  <si>
+    <t>Merge3_build_016_desc</t>
+  </si>
+  <si>
+    <t>ui_map1_icon_magicTree_6</t>
+  </si>
+  <si>
+    <t>花圃7</t>
+  </si>
+  <si>
+    <t>Merge3_build_017</t>
+  </si>
+  <si>
+    <t>Merge3_build_017_desc</t>
+  </si>
+  <si>
+    <t>ui_map1_icon_magicTree_7</t>
+  </si>
+  <si>
+    <t>花圃8</t>
+  </si>
+  <si>
+    <t>Merge3_build_018</t>
+  </si>
+  <si>
+    <t>Merge3_build_018_desc</t>
+  </si>
+  <si>
+    <t>ui_map1_icon_magicTree_8</t>
+  </si>
+  <si>
+    <t>花圃9</t>
+  </si>
+  <si>
+    <t>Merge3_build_019</t>
+  </si>
+  <si>
+    <t>Merge3_build_019_desc</t>
+  </si>
+  <si>
+    <t>2,2</t>
+  </si>
+  <si>
+    <t>ThreeMergeableItem_2_2</t>
+  </si>
+  <si>
+    <t>ui_map1_icon_magicTree_9</t>
   </si>
 </sst>
 </file>
@@ -696,7 +843,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -761,6 +908,36 @@
       </top>
       <bottom style="medium">
         <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
       </bottom>
       <diagonal/>
     </border>
@@ -903,7 +1080,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -915,34 +1092,34 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1027,7 +1204,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1055,20 +1232,50 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1381,8 +1588,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AB4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3"/>
+  <dimension ref="A1:AB13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="14.1111111111111" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" ht="55.95" spans="1:28">
       <c r="A1" s="1" t="s">
@@ -1504,10 +1714,10 @@
       <c r="K2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="L2" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="M2" s="9" t="s">
+      <c r="M2" s="15" t="s">
         <v>29</v>
       </c>
       <c r="N2" s="4" t="s">
@@ -1644,7 +1854,7 @@
     </row>
     <row r="4" ht="25" customHeight="1" spans="1:28">
       <c r="A4" s="7">
-        <v>399999</v>
+        <v>99999</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>61</v>
@@ -1659,23 +1869,23 @@
         <v>1</v>
       </c>
       <c r="F4" s="8">
-        <v>11</v>
-      </c>
-      <c r="G4" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" s="8">
         <v>0</v>
       </c>
       <c r="H4" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="I4" s="10"/>
-      <c r="J4" s="11"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="17"/>
       <c r="K4" s="8" t="s">
         <v>63</v>
       </c>
       <c r="L4" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="M4" s="11"/>
+      <c r="M4" s="17"/>
       <c r="N4" s="8">
         <v>1</v>
       </c>
@@ -1685,28 +1895,648 @@
       <c r="P4" s="8">
         <v>0</v>
       </c>
-      <c r="Q4" s="11"/>
+      <c r="Q4" s="17"/>
       <c r="R4" s="8">
         <v>0</v>
       </c>
-      <c r="S4" s="11"/>
-      <c r="T4" s="8" t="b">
+      <c r="S4" s="17"/>
+      <c r="T4" s="8">
         <v>0</v>
       </c>
       <c r="U4" s="8">
         <v>1</v>
       </c>
-      <c r="V4" s="12"/>
-      <c r="W4" s="11"/>
+      <c r="V4" s="20"/>
+      <c r="W4" s="17"/>
       <c r="X4" s="8">
         <v>2</v>
       </c>
-      <c r="Y4" s="11"/>
-      <c r="Z4" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="11"/>
-      <c r="AB4" s="11"/>
+      <c r="Y4" s="17"/>
+      <c r="Z4" s="22">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="17"/>
+      <c r="AB4" s="17"/>
+    </row>
+    <row r="5" ht="55.95" spans="1:28">
+      <c r="A5" s="9">
+        <v>300028</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="10">
+        <v>1</v>
+      </c>
+      <c r="F5" s="10">
+        <v>2</v>
+      </c>
+      <c r="G5" s="10">
+        <v>1</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="I5" s="10">
+        <v>1</v>
+      </c>
+      <c r="J5" s="10">
+        <v>10</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="L5" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="M5" s="18"/>
+      <c r="N5" s="10">
+        <v>1</v>
+      </c>
+      <c r="O5" s="10">
+        <v>1</v>
+      </c>
+      <c r="P5" s="10">
+        <v>2</v>
+      </c>
+      <c r="Q5" s="18"/>
+      <c r="R5" s="21"/>
+      <c r="S5" s="21"/>
+      <c r="T5" s="10">
+        <v>1</v>
+      </c>
+      <c r="U5" s="10">
+        <v>0</v>
+      </c>
+      <c r="V5" s="21"/>
+      <c r="W5" s="18"/>
+      <c r="X5" s="10">
+        <v>2</v>
+      </c>
+      <c r="Y5" s="21"/>
+      <c r="Z5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="23"/>
+      <c r="AB5" s="23"/>
+    </row>
+    <row r="6" ht="55.95" spans="1:28">
+      <c r="A6" s="13">
+        <v>300029</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" s="14">
+        <v>1</v>
+      </c>
+      <c r="F6" s="14">
+        <v>2</v>
+      </c>
+      <c r="G6" s="14">
+        <v>0</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="I6" s="14">
+        <v>1</v>
+      </c>
+      <c r="J6" s="14">
+        <v>10</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="L6" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="M6" s="18"/>
+      <c r="N6" s="14">
+        <v>2</v>
+      </c>
+      <c r="O6" s="14">
+        <v>2</v>
+      </c>
+      <c r="P6" s="14">
+        <v>5</v>
+      </c>
+      <c r="Q6" s="18"/>
+      <c r="R6" s="19"/>
+      <c r="S6" s="19"/>
+      <c r="T6" s="14">
+        <v>1</v>
+      </c>
+      <c r="U6" s="14">
+        <v>0</v>
+      </c>
+      <c r="V6" s="19"/>
+      <c r="W6" s="18"/>
+      <c r="X6" s="14">
+        <v>2</v>
+      </c>
+      <c r="Y6" s="19"/>
+      <c r="Z6" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="23"/>
+      <c r="AB6" s="23"/>
+    </row>
+    <row r="7" ht="55.95" spans="1:28">
+      <c r="A7" s="13">
+        <v>300030</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E7" s="14">
+        <v>1</v>
+      </c>
+      <c r="F7" s="10">
+        <v>2</v>
+      </c>
+      <c r="G7" s="14">
+        <v>0</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="I7" s="10">
+        <v>1</v>
+      </c>
+      <c r="J7" s="14">
+        <v>10</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="L7" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="M7" s="18"/>
+      <c r="N7" s="14">
+        <v>3</v>
+      </c>
+      <c r="O7" s="14">
+        <v>3</v>
+      </c>
+      <c r="P7" s="14">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="18"/>
+      <c r="R7" s="19"/>
+      <c r="S7" s="19"/>
+      <c r="T7" s="14">
+        <v>1</v>
+      </c>
+      <c r="U7" s="14">
+        <v>0</v>
+      </c>
+      <c r="V7" s="19"/>
+      <c r="W7" s="18"/>
+      <c r="X7" s="14">
+        <v>2</v>
+      </c>
+      <c r="Y7" s="19"/>
+      <c r="Z7" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="23"/>
+      <c r="AB7" s="23"/>
+    </row>
+    <row r="8" ht="55.95" spans="1:28">
+      <c r="A8" s="13">
+        <v>300031</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8" s="14">
+        <v>1</v>
+      </c>
+      <c r="F8" s="14">
+        <v>2</v>
+      </c>
+      <c r="G8" s="14">
+        <v>0</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="I8" s="14">
+        <v>1</v>
+      </c>
+      <c r="J8" s="14">
+        <v>10</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="L8" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="M8" s="18"/>
+      <c r="N8" s="14">
+        <v>4</v>
+      </c>
+      <c r="O8" s="14">
+        <v>4</v>
+      </c>
+      <c r="P8" s="14">
+        <v>30</v>
+      </c>
+      <c r="Q8" s="18"/>
+      <c r="R8" s="14">
+        <v>30</v>
+      </c>
+      <c r="S8" s="19"/>
+      <c r="T8" s="14">
+        <v>1</v>
+      </c>
+      <c r="U8" s="14">
+        <v>0</v>
+      </c>
+      <c r="V8" s="19"/>
+      <c r="W8" s="18"/>
+      <c r="X8" s="14">
+        <v>2</v>
+      </c>
+      <c r="Y8" s="19"/>
+      <c r="Z8" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="23"/>
+      <c r="AB8" s="23"/>
+    </row>
+    <row r="9" ht="55.95" spans="1:28">
+      <c r="A9" s="13">
+        <v>300032</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="E9" s="14">
+        <v>1</v>
+      </c>
+      <c r="F9" s="10">
+        <v>2</v>
+      </c>
+      <c r="G9" s="14">
+        <v>0</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="I9" s="10">
+        <v>1</v>
+      </c>
+      <c r="J9" s="14">
+        <v>10</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="L9" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="M9" s="18"/>
+      <c r="N9" s="14">
+        <v>5</v>
+      </c>
+      <c r="O9" s="14">
+        <v>5</v>
+      </c>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="18"/>
+      <c r="R9" s="14">
+        <v>90</v>
+      </c>
+      <c r="S9" s="14">
+        <v>4701</v>
+      </c>
+      <c r="T9" s="14">
+        <v>1</v>
+      </c>
+      <c r="U9" s="14">
+        <v>0</v>
+      </c>
+      <c r="V9" s="19"/>
+      <c r="W9" s="18"/>
+      <c r="X9" s="14">
+        <v>2</v>
+      </c>
+      <c r="Y9" s="19"/>
+      <c r="Z9" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="23"/>
+      <c r="AB9" s="23"/>
+    </row>
+    <row r="10" ht="55.95" spans="1:28">
+      <c r="A10" s="13">
+        <v>300033</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="E10" s="14">
+        <v>1</v>
+      </c>
+      <c r="F10" s="14">
+        <v>2</v>
+      </c>
+      <c r="G10" s="14">
+        <v>0</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="I10" s="14">
+        <v>1</v>
+      </c>
+      <c r="J10" s="14">
+        <v>10</v>
+      </c>
+      <c r="K10" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="L10" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="M10" s="18"/>
+      <c r="N10" s="14">
+        <v>6</v>
+      </c>
+      <c r="O10" s="14">
+        <v>6</v>
+      </c>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="18"/>
+      <c r="R10" s="14">
+        <v>270</v>
+      </c>
+      <c r="S10" s="14">
+        <v>4702</v>
+      </c>
+      <c r="T10" s="14">
+        <v>1</v>
+      </c>
+      <c r="U10" s="14">
+        <v>0</v>
+      </c>
+      <c r="V10" s="19"/>
+      <c r="W10" s="18"/>
+      <c r="X10" s="14">
+        <v>2</v>
+      </c>
+      <c r="Y10" s="19"/>
+      <c r="Z10" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="23"/>
+      <c r="AB10" s="23"/>
+    </row>
+    <row r="11" ht="55.95" spans="1:28">
+      <c r="A11" s="13">
+        <v>300034</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="E11" s="14">
+        <v>1</v>
+      </c>
+      <c r="F11" s="10">
+        <v>2</v>
+      </c>
+      <c r="G11" s="14">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="I11" s="10">
+        <v>1</v>
+      </c>
+      <c r="J11" s="14">
+        <v>10</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="L11" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="M11" s="18"/>
+      <c r="N11" s="14">
+        <v>7</v>
+      </c>
+      <c r="O11" s="14">
+        <v>7</v>
+      </c>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="18"/>
+      <c r="R11" s="14">
+        <v>810</v>
+      </c>
+      <c r="S11" s="14">
+        <v>4703</v>
+      </c>
+      <c r="T11" s="14">
+        <v>1</v>
+      </c>
+      <c r="U11" s="14">
+        <v>0</v>
+      </c>
+      <c r="V11" s="19"/>
+      <c r="W11" s="18"/>
+      <c r="X11" s="14">
+        <v>2</v>
+      </c>
+      <c r="Y11" s="19"/>
+      <c r="Z11" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="23"/>
+      <c r="AB11" s="23"/>
+    </row>
+    <row r="12" ht="55.95" spans="1:28">
+      <c r="A12" s="13">
+        <v>300035</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12" s="14">
+        <v>1</v>
+      </c>
+      <c r="F12" s="14">
+        <v>2</v>
+      </c>
+      <c r="G12" s="14">
+        <v>0</v>
+      </c>
+      <c r="H12" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="I12" s="14">
+        <v>1</v>
+      </c>
+      <c r="J12" s="14">
+        <v>10</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="L12" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="M12" s="18"/>
+      <c r="N12" s="14">
+        <v>8</v>
+      </c>
+      <c r="O12" s="14">
+        <v>8</v>
+      </c>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="18"/>
+      <c r="R12" s="14">
+        <v>2430</v>
+      </c>
+      <c r="S12" s="14">
+        <v>4704</v>
+      </c>
+      <c r="T12" s="14">
+        <v>1</v>
+      </c>
+      <c r="U12" s="14">
+        <v>0</v>
+      </c>
+      <c r="V12" s="19"/>
+      <c r="W12" s="18"/>
+      <c r="X12" s="14">
+        <v>2</v>
+      </c>
+      <c r="Y12" s="19"/>
+      <c r="Z12" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="23"/>
+      <c r="AB12" s="23"/>
+    </row>
+    <row r="13" ht="55.95" spans="1:28">
+      <c r="A13" s="13">
+        <v>300036</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="E13" s="14">
+        <v>1</v>
+      </c>
+      <c r="F13" s="10">
+        <v>2</v>
+      </c>
+      <c r="G13" s="14">
+        <v>0</v>
+      </c>
+      <c r="H13" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="I13" s="10">
+        <v>1</v>
+      </c>
+      <c r="J13" s="14">
+        <v>10</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="L13" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="M13" s="18"/>
+      <c r="N13" s="14">
+        <v>9</v>
+      </c>
+      <c r="O13" s="14">
+        <v>9</v>
+      </c>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="18"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="14">
+        <v>1</v>
+      </c>
+      <c r="U13" s="14">
+        <v>0</v>
+      </c>
+      <c r="V13" s="19"/>
+      <c r="W13" s="18"/>
+      <c r="X13" s="14">
+        <v>2</v>
+      </c>
+      <c r="Y13" s="19"/>
+      <c r="Z13" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="23"/>
+      <c r="AB13" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/XProject/Assets/ExtraRes/Configs/Excel/MergeableItem.xlsx
+++ b/XProject/Assets/ExtraRes/Configs/Excel/MergeableItem.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="95">
   <si>
     <t>id</t>
   </si>
@@ -144,6 +144,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>1</t>
     </r>
     <r>
@@ -327,10 +333,10 @@
     <t>1,1</t>
   </si>
   <si>
-    <t>ThreeMergeBox</t>
-  </si>
-  <si>
-    <t>test_three_merge_box</t>
+    <t>TripleMergeBox</t>
+  </si>
+  <si>
+    <t>ui_loading_slider_fill</t>
   </si>
   <si>
     <t>花圃1</t>
@@ -342,10 +348,10 @@
     <t>Merge3_build_011_desc</t>
   </si>
   <si>
-    <t>ThreeMergeableItem</t>
-  </si>
-  <si>
-    <t>ui_map1_icon_magicTree_1</t>
+    <t>TripleMergeableItem</t>
+  </si>
+  <si>
+    <t>ui_common_button_rad</t>
   </si>
   <si>
     <t>花圃2</t>
@@ -357,9 +363,6 @@
     <t>Merge3_build_012_desc</t>
   </si>
   <si>
-    <t>ui_map1_icon_magicTree_2</t>
-  </si>
-  <si>
     <t>花圃3</t>
   </si>
   <si>
@@ -369,9 +372,6 @@
     <t>Merge3_build_013_desc</t>
   </si>
   <si>
-    <t>ui_map1_icon_magicTree_3</t>
-  </si>
-  <si>
     <t>花圃4</t>
   </si>
   <si>
@@ -381,9 +381,6 @@
     <t>Merge3_build_014_desc</t>
   </si>
   <si>
-    <t>ui_map1_icon_magicTree_4</t>
-  </si>
-  <si>
     <t>花圃5</t>
   </si>
   <si>
@@ -393,9 +390,6 @@
     <t>Merge3_build_015_desc</t>
   </si>
   <si>
-    <t>ui_map1_icon_magicTree_5</t>
-  </si>
-  <si>
     <t>花圃6</t>
   </si>
   <si>
@@ -405,9 +399,6 @@
     <t>Merge3_build_016_desc</t>
   </si>
   <si>
-    <t>ui_map1_icon_magicTree_6</t>
-  </si>
-  <si>
     <t>花圃7</t>
   </si>
   <si>
@@ -417,9 +408,6 @@
     <t>Merge3_build_017_desc</t>
   </si>
   <si>
-    <t>ui_map1_icon_magicTree_7</t>
-  </si>
-  <si>
     <t>花圃8</t>
   </si>
   <si>
@@ -429,9 +417,6 @@
     <t>Merge3_build_018_desc</t>
   </si>
   <si>
-    <t>ui_map1_icon_magicTree_8</t>
-  </si>
-  <si>
     <t>花圃9</t>
   </si>
   <si>
@@ -442,12 +427,6 @@
   </si>
   <si>
     <t>2,2</t>
-  </si>
-  <si>
-    <t>ThreeMergeableItem_2_2</t>
-  </si>
-  <si>
-    <t>ui_map1_icon_magicTree_9</t>
   </si>
 </sst>
 </file>
@@ -1204,7 +1183,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1262,17 +1241,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
@@ -1906,19 +1879,19 @@
       <c r="U4" s="8">
         <v>1</v>
       </c>
-      <c r="V4" s="20"/>
+      <c r="V4" s="19"/>
       <c r="W4" s="17"/>
       <c r="X4" s="8">
         <v>2</v>
       </c>
       <c r="Y4" s="17"/>
-      <c r="Z4" s="22">
+      <c r="Z4" s="14">
         <v>1</v>
       </c>
       <c r="AA4" s="17"/>
       <c r="AB4" s="17"/>
     </row>
-    <row r="5" ht="55.95" spans="1:28">
+    <row r="5" ht="42.15" spans="1:28">
       <c r="A5" s="9">
         <v>300028</v>
       </c>
@@ -1966,27 +1939,27 @@
         <v>2</v>
       </c>
       <c r="Q5" s="18"/>
-      <c r="R5" s="21"/>
-      <c r="S5" s="21"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="20"/>
       <c r="T5" s="10">
         <v>1</v>
       </c>
       <c r="U5" s="10">
         <v>0</v>
       </c>
-      <c r="V5" s="21"/>
+      <c r="V5" s="20"/>
       <c r="W5" s="18"/>
       <c r="X5" s="10">
         <v>2</v>
       </c>
-      <c r="Y5" s="21"/>
+      <c r="Y5" s="20"/>
       <c r="Z5" s="10">
         <v>0</v>
       </c>
-      <c r="AA5" s="23"/>
-      <c r="AB5" s="23"/>
+      <c r="AA5" s="21"/>
+      <c r="AB5" s="21"/>
     </row>
-    <row r="6" ht="55.95" spans="1:28">
+    <row r="6" ht="42.15" spans="1:28">
       <c r="A6" s="13">
         <v>300029</v>
       </c>
@@ -2017,11 +1990,11 @@
       <c r="J6" s="14">
         <v>10</v>
       </c>
-      <c r="K6" s="14" t="s">
+      <c r="K6" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="L6" s="14" t="s">
-        <v>73</v>
+      <c r="L6" s="10" t="s">
+        <v>69</v>
       </c>
       <c r="M6" s="18"/>
       <c r="N6" s="14">
@@ -2034,38 +2007,38 @@
         <v>5</v>
       </c>
       <c r="Q6" s="18"/>
-      <c r="R6" s="19"/>
-      <c r="S6" s="19"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
       <c r="T6" s="14">
         <v>1</v>
       </c>
       <c r="U6" s="14">
         <v>0</v>
       </c>
-      <c r="V6" s="19"/>
+      <c r="V6" s="17"/>
       <c r="W6" s="18"/>
       <c r="X6" s="14">
         <v>2</v>
       </c>
-      <c r="Y6" s="19"/>
+      <c r="Y6" s="17"/>
       <c r="Z6" s="14">
         <v>0</v>
       </c>
-      <c r="AA6" s="23"/>
-      <c r="AB6" s="23"/>
+      <c r="AA6" s="21"/>
+      <c r="AB6" s="21"/>
     </row>
-    <row r="7" ht="55.95" spans="1:28">
+    <row r="7" ht="42.15" spans="1:28">
       <c r="A7" s="13">
         <v>300030</v>
       </c>
       <c r="B7" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="D7" s="12" t="s">
         <v>75</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>76</v>
       </c>
       <c r="E7" s="14">
         <v>1</v>
@@ -2085,11 +2058,11 @@
       <c r="J7" s="14">
         <v>10</v>
       </c>
-      <c r="K7" s="14" t="s">
+      <c r="K7" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="L7" s="14" t="s">
-        <v>77</v>
+      <c r="L7" s="10" t="s">
+        <v>69</v>
       </c>
       <c r="M7" s="18"/>
       <c r="N7" s="14">
@@ -2102,38 +2075,38 @@
         <v>12</v>
       </c>
       <c r="Q7" s="18"/>
-      <c r="R7" s="19"/>
-      <c r="S7" s="19"/>
+      <c r="R7" s="17"/>
+      <c r="S7" s="17"/>
       <c r="T7" s="14">
         <v>1</v>
       </c>
       <c r="U7" s="14">
         <v>0</v>
       </c>
-      <c r="V7" s="19"/>
+      <c r="V7" s="17"/>
       <c r="W7" s="18"/>
       <c r="X7" s="14">
         <v>2</v>
       </c>
-      <c r="Y7" s="19"/>
+      <c r="Y7" s="17"/>
       <c r="Z7" s="14">
         <v>0</v>
       </c>
-      <c r="AA7" s="23"/>
-      <c r="AB7" s="23"/>
+      <c r="AA7" s="21"/>
+      <c r="AB7" s="21"/>
     </row>
-    <row r="8" ht="55.95" spans="1:28">
+    <row r="8" ht="42.15" spans="1:28">
       <c r="A8" s="13">
         <v>300031</v>
       </c>
       <c r="B8" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="12" t="s">
         <v>78</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>80</v>
       </c>
       <c r="E8" s="14">
         <v>1</v>
@@ -2153,11 +2126,11 @@
       <c r="J8" s="14">
         <v>10</v>
       </c>
-      <c r="K8" s="14" t="s">
+      <c r="K8" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="L8" s="14" t="s">
-        <v>81</v>
+      <c r="L8" s="10" t="s">
+        <v>69</v>
       </c>
       <c r="M8" s="18"/>
       <c r="N8" s="14">
@@ -2173,37 +2146,37 @@
       <c r="R8" s="14">
         <v>30</v>
       </c>
-      <c r="S8" s="19"/>
+      <c r="S8" s="17"/>
       <c r="T8" s="14">
         <v>1</v>
       </c>
       <c r="U8" s="14">
         <v>0</v>
       </c>
-      <c r="V8" s="19"/>
+      <c r="V8" s="17"/>
       <c r="W8" s="18"/>
       <c r="X8" s="14">
         <v>2</v>
       </c>
-      <c r="Y8" s="19"/>
+      <c r="Y8" s="17"/>
       <c r="Z8" s="14">
         <v>0</v>
       </c>
-      <c r="AA8" s="23"/>
-      <c r="AB8" s="23"/>
+      <c r="AA8" s="21"/>
+      <c r="AB8" s="21"/>
     </row>
-    <row r="9" ht="55.95" spans="1:28">
+    <row r="9" ht="42.15" spans="1:28">
       <c r="A9" s="13">
         <v>300032</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E9" s="14">
         <v>1</v>
@@ -2223,11 +2196,11 @@
       <c r="J9" s="14">
         <v>10</v>
       </c>
-      <c r="K9" s="14" t="s">
+      <c r="K9" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="L9" s="14" t="s">
-        <v>85</v>
+      <c r="L9" s="10" t="s">
+        <v>69</v>
       </c>
       <c r="M9" s="18"/>
       <c r="N9" s="14">
@@ -2236,7 +2209,7 @@
       <c r="O9" s="14">
         <v>5</v>
       </c>
-      <c r="P9" s="19"/>
+      <c r="P9" s="17"/>
       <c r="Q9" s="18"/>
       <c r="R9" s="14">
         <v>90</v>
@@ -2250,30 +2223,30 @@
       <c r="U9" s="14">
         <v>0</v>
       </c>
-      <c r="V9" s="19"/>
+      <c r="V9" s="17"/>
       <c r="W9" s="18"/>
       <c r="X9" s="14">
         <v>2</v>
       </c>
-      <c r="Y9" s="19"/>
+      <c r="Y9" s="17"/>
       <c r="Z9" s="14">
         <v>0</v>
       </c>
-      <c r="AA9" s="23"/>
-      <c r="AB9" s="23"/>
+      <c r="AA9" s="21"/>
+      <c r="AB9" s="21"/>
     </row>
-    <row r="10" ht="55.95" spans="1:28">
+    <row r="10" ht="42.15" spans="1:28">
       <c r="A10" s="13">
         <v>300033</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E10" s="14">
         <v>1</v>
@@ -2293,11 +2266,11 @@
       <c r="J10" s="14">
         <v>10</v>
       </c>
-      <c r="K10" s="14" t="s">
+      <c r="K10" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="L10" s="14" t="s">
-        <v>89</v>
+      <c r="L10" s="10" t="s">
+        <v>69</v>
       </c>
       <c r="M10" s="18"/>
       <c r="N10" s="14">
@@ -2306,7 +2279,7 @@
       <c r="O10" s="14">
         <v>6</v>
       </c>
-      <c r="P10" s="19"/>
+      <c r="P10" s="17"/>
       <c r="Q10" s="18"/>
       <c r="R10" s="14">
         <v>270</v>
@@ -2320,30 +2293,30 @@
       <c r="U10" s="14">
         <v>0</v>
       </c>
-      <c r="V10" s="19"/>
+      <c r="V10" s="17"/>
       <c r="W10" s="18"/>
       <c r="X10" s="14">
         <v>2</v>
       </c>
-      <c r="Y10" s="19"/>
+      <c r="Y10" s="17"/>
       <c r="Z10" s="14">
         <v>0</v>
       </c>
-      <c r="AA10" s="23"/>
-      <c r="AB10" s="23"/>
+      <c r="AA10" s="21"/>
+      <c r="AB10" s="21"/>
     </row>
-    <row r="11" ht="55.95" spans="1:28">
+    <row r="11" ht="42.15" spans="1:28">
       <c r="A11" s="13">
         <v>300034</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E11" s="14">
         <v>1</v>
@@ -2363,11 +2336,11 @@
       <c r="J11" s="14">
         <v>10</v>
       </c>
-      <c r="K11" s="14" t="s">
+      <c r="K11" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="L11" s="14" t="s">
-        <v>93</v>
+      <c r="L11" s="10" t="s">
+        <v>69</v>
       </c>
       <c r="M11" s="18"/>
       <c r="N11" s="14">
@@ -2376,7 +2349,7 @@
       <c r="O11" s="14">
         <v>7</v>
       </c>
-      <c r="P11" s="19"/>
+      <c r="P11" s="17"/>
       <c r="Q11" s="18"/>
       <c r="R11" s="14">
         <v>810</v>
@@ -2390,30 +2363,30 @@
       <c r="U11" s="14">
         <v>0</v>
       </c>
-      <c r="V11" s="19"/>
+      <c r="V11" s="17"/>
       <c r="W11" s="18"/>
       <c r="X11" s="14">
         <v>2</v>
       </c>
-      <c r="Y11" s="19"/>
+      <c r="Y11" s="17"/>
       <c r="Z11" s="14">
         <v>0</v>
       </c>
-      <c r="AA11" s="23"/>
-      <c r="AB11" s="23"/>
+      <c r="AA11" s="21"/>
+      <c r="AB11" s="21"/>
     </row>
-    <row r="12" ht="55.95" spans="1:28">
+    <row r="12" ht="42.15" spans="1:28">
       <c r="A12" s="13">
         <v>300035</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E12" s="14">
         <v>1</v>
@@ -2433,11 +2406,11 @@
       <c r="J12" s="14">
         <v>10</v>
       </c>
-      <c r="K12" s="14" t="s">
+      <c r="K12" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="L12" s="14" t="s">
-        <v>97</v>
+      <c r="L12" s="10" t="s">
+        <v>69</v>
       </c>
       <c r="M12" s="18"/>
       <c r="N12" s="14">
@@ -2446,7 +2419,7 @@
       <c r="O12" s="14">
         <v>8</v>
       </c>
-      <c r="P12" s="19"/>
+      <c r="P12" s="17"/>
       <c r="Q12" s="18"/>
       <c r="R12" s="14">
         <v>2430</v>
@@ -2460,30 +2433,30 @@
       <c r="U12" s="14">
         <v>0</v>
       </c>
-      <c r="V12" s="19"/>
+      <c r="V12" s="17"/>
       <c r="W12" s="18"/>
       <c r="X12" s="14">
         <v>2</v>
       </c>
-      <c r="Y12" s="19"/>
+      <c r="Y12" s="17"/>
       <c r="Z12" s="14">
         <v>0</v>
       </c>
-      <c r="AA12" s="23"/>
-      <c r="AB12" s="23"/>
+      <c r="AA12" s="21"/>
+      <c r="AB12" s="21"/>
     </row>
-    <row r="13" ht="55.95" spans="1:28">
+    <row r="13" ht="42.15" spans="1:28">
       <c r="A13" s="13">
         <v>300036</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="E13" s="14">
         <v>1</v>
@@ -2495,7 +2468,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="I13" s="10">
         <v>1</v>
@@ -2503,11 +2476,11 @@
       <c r="J13" s="14">
         <v>10</v>
       </c>
-      <c r="K13" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="L13" s="14" t="s">
-        <v>103</v>
+      <c r="K13" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="L13" s="10" t="s">
+        <v>69</v>
       </c>
       <c r="M13" s="18"/>
       <c r="N13" s="14">
@@ -2516,27 +2489,27 @@
       <c r="O13" s="14">
         <v>9</v>
       </c>
-      <c r="P13" s="19"/>
+      <c r="P13" s="17"/>
       <c r="Q13" s="18"/>
-      <c r="R13" s="19"/>
-      <c r="S13" s="19"/>
+      <c r="R13" s="17"/>
+      <c r="S13" s="17"/>
       <c r="T13" s="14">
         <v>1</v>
       </c>
       <c r="U13" s="14">
         <v>0</v>
       </c>
-      <c r="V13" s="19"/>
+      <c r="V13" s="17"/>
       <c r="W13" s="18"/>
       <c r="X13" s="14">
         <v>2</v>
       </c>
-      <c r="Y13" s="19"/>
+      <c r="Y13" s="17"/>
       <c r="Z13" s="14">
         <v>0</v>
       </c>
-      <c r="AA13" s="23"/>
-      <c r="AB13" s="23"/>
+      <c r="AA13" s="21"/>
+      <c r="AB13" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/XProject/Assets/ExtraRes/Configs/Excel/MergeableItem.xlsx
+++ b/XProject/Assets/ExtraRes/Configs/Excel/MergeableItem.xlsx
@@ -7,7 +7,8 @@
     <workbookView windowWidth="29868" windowHeight="13380"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="MerageableItem" sheetId="1" r:id="rId1"/>
+    <sheet name="ChestIncludeRewards" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="114">
   <si>
     <t>id</t>
   </si>
@@ -351,7 +352,7 @@
     <t>TripleMergeableItem</t>
   </si>
   <si>
-    <t>ui_common_button_rad</t>
+    <t>01</t>
   </si>
   <si>
     <t>花圃2</t>
@@ -363,6 +364,9 @@
     <t>Merge3_build_012_desc</t>
   </si>
   <si>
+    <t>02</t>
+  </si>
+  <si>
     <t>花圃3</t>
   </si>
   <si>
@@ -372,6 +376,9 @@
     <t>Merge3_build_013_desc</t>
   </si>
   <si>
+    <t>03</t>
+  </si>
+  <si>
     <t>花圃4</t>
   </si>
   <si>
@@ -381,6 +388,9 @@
     <t>Merge3_build_014_desc</t>
   </si>
   <si>
+    <t>04</t>
+  </si>
+  <si>
     <t>花圃5</t>
   </si>
   <si>
@@ -390,6 +400,9 @@
     <t>Merge3_build_015_desc</t>
   </si>
   <si>
+    <t>05</t>
+  </si>
+  <si>
     <t>花圃6</t>
   </si>
   <si>
@@ -399,6 +412,9 @@
     <t>Merge3_build_016_desc</t>
   </si>
   <si>
+    <t>06</t>
+  </si>
+  <si>
     <t>花圃7</t>
   </si>
   <si>
@@ -408,6 +424,9 @@
     <t>Merge3_build_017_desc</t>
   </si>
   <si>
+    <t>07</t>
+  </si>
+  <si>
     <t>花圃8</t>
   </si>
   <si>
@@ -417,6 +436,9 @@
     <t>Merge3_build_018_desc</t>
   </si>
   <si>
+    <t>08</t>
+  </si>
+  <si>
     <t>花圃9</t>
   </si>
   <si>
@@ -427,6 +449,42 @@
   </si>
   <si>
     <t>2,2</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>index</t>
+  </si>
+  <si>
+    <t>rewards</t>
+  </si>
+  <si>
+    <t>targetPlaceAreaId</t>
+  </si>
+  <si>
+    <t>targetPlaceCells</t>
+  </si>
+  <si>
+    <t>guidanceId</t>
+  </si>
+  <si>
+    <t>第几次开启</t>
+  </si>
+  <si>
+    <t>开出奖励</t>
+  </si>
+  <si>
+    <t>开出物品目标放置区域id(mapArea)</t>
+  </si>
+  <si>
+    <t>开出物品目标放置地块坐标列表</t>
+  </si>
+  <si>
+    <t>宝箱开启后要执行的引导</t>
+  </si>
+  <si>
+    <t>5,11;6,11;8,11;5,10;6,10;5,8</t>
   </si>
 </sst>
 </file>
@@ -454,6 +512,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -462,12 +526,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
@@ -1183,7 +1241,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1199,10 +1257,22 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1223,32 +1293,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1687,10 +1751,10 @@
       <c r="K2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="L2" s="15" t="s">
+      <c r="L2" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="M2" s="15" t="s">
+      <c r="M2" s="17" t="s">
         <v>29</v>
       </c>
       <c r="N2" s="4" t="s">
@@ -1755,10 +1819,10 @@
       <c r="E3" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="10" t="s">
         <v>39</v>
       </c>
       <c r="H3" s="4" t="s">
@@ -1800,7 +1864,7 @@
       <c r="T3" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="U3" s="6" t="s">
+      <c r="U3" s="10" t="s">
         <v>53</v>
       </c>
       <c r="V3" s="4" t="s">
@@ -1826,694 +1890,955 @@
       </c>
     </row>
     <row r="4" ht="25" customHeight="1" spans="1:28">
-      <c r="A4" s="7">
+      <c r="A4" s="11">
         <v>99999</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="12">
         <v>101</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="12">
         <v>101</v>
       </c>
-      <c r="E4" s="8">
-        <v>1</v>
-      </c>
-      <c r="F4" s="8">
-        <v>1</v>
-      </c>
-      <c r="G4" s="8">
-        <v>0</v>
-      </c>
-      <c r="H4" s="8" t="s">
+      <c r="E4" s="12">
+        <v>1</v>
+      </c>
+      <c r="F4" s="12">
+        <v>1</v>
+      </c>
+      <c r="G4" s="12">
+        <v>0</v>
+      </c>
+      <c r="H4" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="I4" s="16"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="8" t="s">
+      <c r="I4" s="18"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="L4" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="M4" s="17"/>
-      <c r="N4" s="8">
-        <v>1</v>
-      </c>
-      <c r="O4" s="8">
-        <v>0</v>
-      </c>
-      <c r="P4" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="8">
-        <v>0</v>
-      </c>
-      <c r="S4" s="17"/>
-      <c r="T4" s="8">
-        <v>0</v>
-      </c>
-      <c r="U4" s="8">
-        <v>1</v>
-      </c>
-      <c r="V4" s="19"/>
-      <c r="W4" s="17"/>
-      <c r="X4" s="8">
+      <c r="M4" s="6"/>
+      <c r="N4" s="12">
+        <v>1</v>
+      </c>
+      <c r="O4" s="12">
+        <v>0</v>
+      </c>
+      <c r="P4" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="12">
+        <v>0</v>
+      </c>
+      <c r="S4" s="6"/>
+      <c r="T4" s="12">
+        <v>0</v>
+      </c>
+      <c r="U4" s="12">
+        <v>1</v>
+      </c>
+      <c r="V4" s="20"/>
+      <c r="W4" s="6"/>
+      <c r="X4" s="12">
         <v>2</v>
       </c>
-      <c r="Y4" s="17"/>
-      <c r="Z4" s="14">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="17"/>
-      <c r="AB4" s="17"/>
+      <c r="Y4" s="6"/>
+      <c r="Z4" s="8">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="6"/>
+      <c r="AB4" s="6"/>
     </row>
     <row r="5" ht="42.15" spans="1:28">
-      <c r="A5" s="9">
+      <c r="A5" s="13">
         <v>300028</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="10">
-        <v>1</v>
-      </c>
-      <c r="F5" s="10">
+      <c r="E5" s="14">
+        <v>1</v>
+      </c>
+      <c r="F5" s="14">
         <v>2</v>
       </c>
-      <c r="G5" s="10">
-        <v>1</v>
-      </c>
-      <c r="H5" s="10" t="s">
+      <c r="G5" s="14">
+        <v>1</v>
+      </c>
+      <c r="H5" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="I5" s="10">
-        <v>1</v>
-      </c>
-      <c r="J5" s="10">
+      <c r="I5" s="14">
+        <v>1</v>
+      </c>
+      <c r="J5" s="14">
         <v>10</v>
       </c>
-      <c r="K5" s="10" t="s">
+      <c r="K5" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="L5" s="10" t="s">
+      <c r="L5" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="M5" s="18"/>
-      <c r="N5" s="10">
-        <v>1</v>
-      </c>
-      <c r="O5" s="10">
-        <v>1</v>
-      </c>
-      <c r="P5" s="10">
+      <c r="M5" s="19"/>
+      <c r="N5" s="14">
+        <v>1</v>
+      </c>
+      <c r="O5" s="14">
+        <v>1</v>
+      </c>
+      <c r="P5" s="14">
         <v>2</v>
       </c>
-      <c r="Q5" s="18"/>
-      <c r="R5" s="20"/>
-      <c r="S5" s="20"/>
-      <c r="T5" s="10">
-        <v>1</v>
-      </c>
-      <c r="U5" s="10">
-        <v>0</v>
-      </c>
-      <c r="V5" s="20"/>
-      <c r="W5" s="18"/>
-      <c r="X5" s="10">
+      <c r="Q5" s="19"/>
+      <c r="R5" s="21"/>
+      <c r="S5" s="21"/>
+      <c r="T5" s="14">
+        <v>1</v>
+      </c>
+      <c r="U5" s="14">
+        <v>0</v>
+      </c>
+      <c r="V5" s="21"/>
+      <c r="W5" s="19"/>
+      <c r="X5" s="14">
         <v>2</v>
       </c>
-      <c r="Y5" s="20"/>
-      <c r="Z5" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="21"/>
-      <c r="AB5" s="21"/>
+      <c r="Y5" s="21"/>
+      <c r="Z5" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="22"/>
+      <c r="AB5" s="22"/>
     </row>
     <row r="6" ht="42.15" spans="1:28">
-      <c r="A6" s="13">
+      <c r="A6" s="5">
         <v>300029</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="14">
-        <v>1</v>
-      </c>
-      <c r="F6" s="14">
+      <c r="E6" s="8">
+        <v>1</v>
+      </c>
+      <c r="F6" s="8">
         <v>2</v>
       </c>
-      <c r="G6" s="14">
-        <v>0</v>
-      </c>
-      <c r="H6" s="14" t="s">
+      <c r="G6" s="8">
+        <v>0</v>
+      </c>
+      <c r="H6" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="I6" s="14">
-        <v>1</v>
-      </c>
-      <c r="J6" s="14">
+      <c r="I6" s="8">
+        <v>1</v>
+      </c>
+      <c r="J6" s="8">
         <v>10</v>
       </c>
-      <c r="K6" s="10" t="s">
+      <c r="K6" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="L6" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="M6" s="18"/>
-      <c r="N6" s="14">
+      <c r="L6" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="M6" s="19"/>
+      <c r="N6" s="8">
         <v>2</v>
       </c>
-      <c r="O6" s="14">
+      <c r="O6" s="8">
         <v>2</v>
       </c>
-      <c r="P6" s="14">
+      <c r="P6" s="8">
         <v>5</v>
       </c>
-      <c r="Q6" s="18"/>
-      <c r="R6" s="17"/>
-      <c r="S6" s="17"/>
-      <c r="T6" s="14">
-        <v>1</v>
-      </c>
-      <c r="U6" s="14">
-        <v>0</v>
-      </c>
-      <c r="V6" s="17"/>
-      <c r="W6" s="18"/>
-      <c r="X6" s="14">
+      <c r="Q6" s="19"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="6"/>
+      <c r="T6" s="8">
+        <v>1</v>
+      </c>
+      <c r="U6" s="8">
+        <v>0</v>
+      </c>
+      <c r="V6" s="6"/>
+      <c r="W6" s="19"/>
+      <c r="X6" s="8">
         <v>2</v>
       </c>
-      <c r="Y6" s="17"/>
-      <c r="Z6" s="14">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="21"/>
-      <c r="AB6" s="21"/>
+      <c r="Y6" s="6"/>
+      <c r="Z6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="22"/>
+      <c r="AB6" s="22"/>
     </row>
     <row r="7" ht="42.15" spans="1:28">
-      <c r="A7" s="13">
+      <c r="A7" s="5">
         <v>300030</v>
       </c>
-      <c r="B7" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" s="11" t="s">
+      <c r="B7" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="C7" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="E7" s="14">
-        <v>1</v>
-      </c>
-      <c r="F7" s="10">
+      <c r="D7" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="E7" s="8">
+        <v>1</v>
+      </c>
+      <c r="F7" s="14">
         <v>2</v>
       </c>
-      <c r="G7" s="14">
-        <v>0</v>
-      </c>
-      <c r="H7" s="14" t="s">
+      <c r="G7" s="8">
+        <v>0</v>
+      </c>
+      <c r="H7" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="I7" s="10">
-        <v>1</v>
-      </c>
-      <c r="J7" s="14">
+      <c r="I7" s="14">
+        <v>1</v>
+      </c>
+      <c r="J7" s="8">
         <v>10</v>
       </c>
-      <c r="K7" s="10" t="s">
+      <c r="K7" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="L7" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="M7" s="18"/>
-      <c r="N7" s="14">
+      <c r="L7" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="M7" s="19"/>
+      <c r="N7" s="8">
         <v>3</v>
       </c>
-      <c r="O7" s="14">
+      <c r="O7" s="8">
         <v>3</v>
       </c>
-      <c r="P7" s="14">
+      <c r="P7" s="8">
         <v>12</v>
       </c>
-      <c r="Q7" s="18"/>
-      <c r="R7" s="17"/>
-      <c r="S7" s="17"/>
-      <c r="T7" s="14">
-        <v>1</v>
-      </c>
-      <c r="U7" s="14">
-        <v>0</v>
-      </c>
-      <c r="V7" s="17"/>
-      <c r="W7" s="18"/>
-      <c r="X7" s="14">
+      <c r="Q7" s="19"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="8">
+        <v>1</v>
+      </c>
+      <c r="U7" s="8">
+        <v>0</v>
+      </c>
+      <c r="V7" s="6"/>
+      <c r="W7" s="19"/>
+      <c r="X7" s="8">
         <v>2</v>
       </c>
-      <c r="Y7" s="17"/>
-      <c r="Z7" s="14">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="21"/>
-      <c r="AB7" s="21"/>
+      <c r="Y7" s="6"/>
+      <c r="Z7" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="22"/>
+      <c r="AB7" s="22"/>
     </row>
     <row r="8" ht="42.15" spans="1:28">
-      <c r="A8" s="13">
+      <c r="A8" s="5">
         <v>300031</v>
       </c>
-      <c r="B8" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="D8" s="12" t="s">
+      <c r="B8" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="E8" s="14">
-        <v>1</v>
-      </c>
-      <c r="F8" s="14">
+      <c r="C8" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8" s="8">
+        <v>1</v>
+      </c>
+      <c r="F8" s="8">
         <v>2</v>
       </c>
-      <c r="G8" s="14">
-        <v>0</v>
-      </c>
-      <c r="H8" s="14" t="s">
+      <c r="G8" s="8">
+        <v>0</v>
+      </c>
+      <c r="H8" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="I8" s="14">
-        <v>1</v>
-      </c>
-      <c r="J8" s="14">
+      <c r="I8" s="8">
+        <v>1</v>
+      </c>
+      <c r="J8" s="8">
         <v>10</v>
       </c>
-      <c r="K8" s="10" t="s">
+      <c r="K8" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="L8" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="M8" s="18"/>
-      <c r="N8" s="14">
+      <c r="L8" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="M8" s="19"/>
+      <c r="N8" s="8">
         <v>4</v>
       </c>
-      <c r="O8" s="14">
+      <c r="O8" s="8">
         <v>4</v>
       </c>
-      <c r="P8" s="14">
+      <c r="P8" s="8">
         <v>30</v>
       </c>
-      <c r="Q8" s="18"/>
-      <c r="R8" s="14">
+      <c r="Q8" s="19"/>
+      <c r="R8" s="8">
         <v>30</v>
       </c>
-      <c r="S8" s="17"/>
-      <c r="T8" s="14">
-        <v>1</v>
-      </c>
-      <c r="U8" s="14">
-        <v>0</v>
-      </c>
-      <c r="V8" s="17"/>
-      <c r="W8" s="18"/>
-      <c r="X8" s="14">
+      <c r="S8" s="6"/>
+      <c r="T8" s="8">
+        <v>1</v>
+      </c>
+      <c r="U8" s="8">
+        <v>0</v>
+      </c>
+      <c r="V8" s="6"/>
+      <c r="W8" s="19"/>
+      <c r="X8" s="8">
         <v>2</v>
       </c>
-      <c r="Y8" s="17"/>
-      <c r="Z8" s="14">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="21"/>
-      <c r="AB8" s="21"/>
+      <c r="Y8" s="6"/>
+      <c r="Z8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="22"/>
+      <c r="AB8" s="22"/>
     </row>
     <row r="9" ht="42.15" spans="1:28">
-      <c r="A9" s="13">
+      <c r="A9" s="5">
         <v>300032</v>
       </c>
-      <c r="B9" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="E9" s="14">
-        <v>1</v>
-      </c>
-      <c r="F9" s="10">
+      <c r="B9" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="E9" s="8">
+        <v>1</v>
+      </c>
+      <c r="F9" s="14">
         <v>2</v>
       </c>
-      <c r="G9" s="14">
-        <v>0</v>
-      </c>
-      <c r="H9" s="14" t="s">
+      <c r="G9" s="8">
+        <v>0</v>
+      </c>
+      <c r="H9" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="I9" s="10">
-        <v>1</v>
-      </c>
-      <c r="J9" s="14">
+      <c r="I9" s="14">
+        <v>1</v>
+      </c>
+      <c r="J9" s="8">
         <v>10</v>
       </c>
-      <c r="K9" s="10" t="s">
+      <c r="K9" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="L9" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="M9" s="18"/>
-      <c r="N9" s="14">
+      <c r="L9" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="M9" s="19"/>
+      <c r="N9" s="8">
         <v>5</v>
       </c>
-      <c r="O9" s="14">
+      <c r="O9" s="8">
         <v>5</v>
       </c>
-      <c r="P9" s="17"/>
-      <c r="Q9" s="18"/>
-      <c r="R9" s="14">
+      <c r="P9" s="6"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="8">
         <v>90</v>
       </c>
-      <c r="S9" s="14">
+      <c r="S9" s="8">
         <v>4701</v>
       </c>
-      <c r="T9" s="14">
-        <v>1</v>
-      </c>
-      <c r="U9" s="14">
-        <v>0</v>
-      </c>
-      <c r="V9" s="17"/>
-      <c r="W9" s="18"/>
-      <c r="X9" s="14">
+      <c r="T9" s="8">
+        <v>1</v>
+      </c>
+      <c r="U9" s="8">
+        <v>0</v>
+      </c>
+      <c r="V9" s="6"/>
+      <c r="W9" s="19"/>
+      <c r="X9" s="8">
         <v>2</v>
       </c>
-      <c r="Y9" s="17"/>
-      <c r="Z9" s="14">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="21"/>
-      <c r="AB9" s="21"/>
+      <c r="Y9" s="6"/>
+      <c r="Z9" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="22"/>
+      <c r="AB9" s="22"/>
     </row>
     <row r="10" ht="42.15" spans="1:28">
-      <c r="A10" s="13">
+      <c r="A10" s="5">
         <v>300033</v>
       </c>
-      <c r="B10" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="E10" s="14">
-        <v>1</v>
-      </c>
-      <c r="F10" s="14">
+      <c r="B10" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="E10" s="8">
+        <v>1</v>
+      </c>
+      <c r="F10" s="8">
         <v>2</v>
       </c>
-      <c r="G10" s="14">
-        <v>0</v>
-      </c>
-      <c r="H10" s="14" t="s">
+      <c r="G10" s="8">
+        <v>0</v>
+      </c>
+      <c r="H10" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="I10" s="14">
-        <v>1</v>
-      </c>
-      <c r="J10" s="14">
+      <c r="I10" s="8">
+        <v>1</v>
+      </c>
+      <c r="J10" s="8">
         <v>10</v>
       </c>
-      <c r="K10" s="10" t="s">
+      <c r="K10" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="L10" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="M10" s="18"/>
-      <c r="N10" s="14">
+      <c r="L10" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="M10" s="19"/>
+      <c r="N10" s="8">
         <v>6</v>
       </c>
-      <c r="O10" s="14">
+      <c r="O10" s="8">
         <v>6</v>
       </c>
-      <c r="P10" s="17"/>
-      <c r="Q10" s="18"/>
-      <c r="R10" s="14">
+      <c r="P10" s="6"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="8">
         <v>270</v>
       </c>
-      <c r="S10" s="14">
+      <c r="S10" s="8">
         <v>4702</v>
       </c>
-      <c r="T10" s="14">
-        <v>1</v>
-      </c>
-      <c r="U10" s="14">
-        <v>0</v>
-      </c>
-      <c r="V10" s="17"/>
-      <c r="W10" s="18"/>
-      <c r="X10" s="14">
+      <c r="T10" s="8">
+        <v>1</v>
+      </c>
+      <c r="U10" s="8">
+        <v>0</v>
+      </c>
+      <c r="V10" s="6"/>
+      <c r="W10" s="19"/>
+      <c r="X10" s="8">
         <v>2</v>
       </c>
-      <c r="Y10" s="17"/>
-      <c r="Z10" s="14">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="21"/>
-      <c r="AB10" s="21"/>
+      <c r="Y10" s="6"/>
+      <c r="Z10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="22"/>
+      <c r="AB10" s="22"/>
     </row>
     <row r="11" ht="42.15" spans="1:28">
-      <c r="A11" s="13">
+      <c r="A11" s="5">
         <v>300034</v>
       </c>
-      <c r="B11" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="E11" s="14">
-        <v>1</v>
-      </c>
-      <c r="F11" s="10">
+      <c r="B11" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1</v>
+      </c>
+      <c r="F11" s="14">
         <v>2</v>
       </c>
-      <c r="G11" s="14">
-        <v>0</v>
-      </c>
-      <c r="H11" s="14" t="s">
+      <c r="G11" s="8">
+        <v>0</v>
+      </c>
+      <c r="H11" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="I11" s="10">
-        <v>1</v>
-      </c>
-      <c r="J11" s="14">
+      <c r="I11" s="14">
+        <v>1</v>
+      </c>
+      <c r="J11" s="8">
         <v>10</v>
       </c>
-      <c r="K11" s="10" t="s">
+      <c r="K11" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="L11" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="M11" s="18"/>
-      <c r="N11" s="14">
+      <c r="L11" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="M11" s="19"/>
+      <c r="N11" s="8">
         <v>7</v>
       </c>
-      <c r="O11" s="14">
+      <c r="O11" s="8">
         <v>7</v>
       </c>
-      <c r="P11" s="17"/>
-      <c r="Q11" s="18"/>
-      <c r="R11" s="14">
+      <c r="P11" s="6"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="8">
         <v>810</v>
       </c>
-      <c r="S11" s="14">
+      <c r="S11" s="8">
         <v>4703</v>
       </c>
-      <c r="T11" s="14">
-        <v>1</v>
-      </c>
-      <c r="U11" s="14">
-        <v>0</v>
-      </c>
-      <c r="V11" s="17"/>
-      <c r="W11" s="18"/>
-      <c r="X11" s="14">
+      <c r="T11" s="8">
+        <v>1</v>
+      </c>
+      <c r="U11" s="8">
+        <v>0</v>
+      </c>
+      <c r="V11" s="6"/>
+      <c r="W11" s="19"/>
+      <c r="X11" s="8">
         <v>2</v>
       </c>
-      <c r="Y11" s="17"/>
-      <c r="Z11" s="14">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="21"/>
-      <c r="AB11" s="21"/>
+      <c r="Y11" s="6"/>
+      <c r="Z11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="22"/>
+      <c r="AB11" s="22"/>
     </row>
     <row r="12" ht="42.15" spans="1:28">
-      <c r="A12" s="13">
+      <c r="A12" s="5">
         <v>300035</v>
       </c>
-      <c r="B12" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="E12" s="14">
-        <v>1</v>
-      </c>
-      <c r="F12" s="14">
+      <c r="B12" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12" s="8">
+        <v>1</v>
+      </c>
+      <c r="F12" s="8">
         <v>2</v>
       </c>
-      <c r="G12" s="14">
-        <v>0</v>
-      </c>
-      <c r="H12" s="14" t="s">
+      <c r="G12" s="8">
+        <v>0</v>
+      </c>
+      <c r="H12" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="I12" s="14">
-        <v>1</v>
-      </c>
-      <c r="J12" s="14">
+      <c r="I12" s="8">
+        <v>1</v>
+      </c>
+      <c r="J12" s="8">
         <v>10</v>
       </c>
-      <c r="K12" s="10" t="s">
+      <c r="K12" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="L12" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="M12" s="18"/>
-      <c r="N12" s="14">
+      <c r="L12" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="M12" s="19"/>
+      <c r="N12" s="8">
         <v>8</v>
       </c>
-      <c r="O12" s="14">
+      <c r="O12" s="8">
         <v>8</v>
       </c>
-      <c r="P12" s="17"/>
-      <c r="Q12" s="18"/>
-      <c r="R12" s="14">
+      <c r="P12" s="6"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="8">
         <v>2430</v>
       </c>
-      <c r="S12" s="14">
+      <c r="S12" s="8">
         <v>4704</v>
       </c>
-      <c r="T12" s="14">
-        <v>1</v>
-      </c>
-      <c r="U12" s="14">
-        <v>0</v>
-      </c>
-      <c r="V12" s="17"/>
-      <c r="W12" s="18"/>
-      <c r="X12" s="14">
+      <c r="T12" s="8">
+        <v>1</v>
+      </c>
+      <c r="U12" s="8">
+        <v>0</v>
+      </c>
+      <c r="V12" s="6"/>
+      <c r="W12" s="19"/>
+      <c r="X12" s="8">
         <v>2</v>
       </c>
-      <c r="Y12" s="17"/>
-      <c r="Z12" s="14">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="21"/>
-      <c r="AB12" s="21"/>
+      <c r="Y12" s="6"/>
+      <c r="Z12" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="22"/>
+      <c r="AB12" s="22"/>
     </row>
     <row r="13" ht="42.15" spans="1:28">
-      <c r="A13" s="13">
+      <c r="A13" s="5">
         <v>300036</v>
       </c>
-      <c r="B13" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="E13" s="14">
-        <v>1</v>
-      </c>
-      <c r="F13" s="10">
+      <c r="B13" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="E13" s="8">
+        <v>1</v>
+      </c>
+      <c r="F13" s="14">
         <v>2</v>
       </c>
-      <c r="G13" s="14">
-        <v>0</v>
-      </c>
-      <c r="H13" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="I13" s="10">
-        <v>1</v>
-      </c>
-      <c r="J13" s="14">
+      <c r="G13" s="8">
+        <v>0</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="I13" s="14">
+        <v>1</v>
+      </c>
+      <c r="J13" s="8">
         <v>10</v>
       </c>
-      <c r="K13" s="10" t="s">
+      <c r="K13" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="L13" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="M13" s="18"/>
-      <c r="N13" s="14">
+      <c r="L13" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="M13" s="19"/>
+      <c r="N13" s="8">
         <v>9</v>
       </c>
-      <c r="O13" s="14">
+      <c r="O13" s="8">
         <v>9</v>
       </c>
-      <c r="P13" s="17"/>
-      <c r="Q13" s="18"/>
-      <c r="R13" s="17"/>
-      <c r="S13" s="17"/>
-      <c r="T13" s="14">
-        <v>1</v>
-      </c>
-      <c r="U13" s="14">
-        <v>0</v>
-      </c>
-      <c r="V13" s="17"/>
-      <c r="W13" s="18"/>
-      <c r="X13" s="14">
+      <c r="P13" s="6"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="6"/>
+      <c r="S13" s="6"/>
+      <c r="T13" s="8">
+        <v>1</v>
+      </c>
+      <c r="U13" s="8">
+        <v>0</v>
+      </c>
+      <c r="V13" s="6"/>
+      <c r="W13" s="19"/>
+      <c r="X13" s="8">
         <v>2</v>
       </c>
-      <c r="Y13" s="17"/>
-      <c r="Z13" s="14">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="21"/>
-      <c r="AB13" s="21"/>
+      <c r="Y13" s="6"/>
+      <c r="Z13" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="22"/>
+      <c r="AB13" s="22"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <cols>
+    <col min="3" max="3" width="87.5555555555556" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28.35" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" ht="15.15" spans="1:6">
+      <c r="A2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" ht="71.55" spans="1:6">
+      <c r="A3" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" ht="55.95" spans="1:6">
+      <c r="A4" s="5">
+        <v>1</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="7">
+        <v>3.000283000283e+35</v>
+      </c>
+      <c r="D4" s="8">
+        <v>1</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="F4" s="8">
+        <v>300062</v>
+      </c>
+    </row>
+    <row r="5" ht="15.15" spans="1:6">
+      <c r="A5" s="5">
+        <v>2</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="7">
+        <v>3.000283000283e+41</v>
+      </c>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+    </row>
+    <row r="6" ht="15.15" spans="1:6">
+      <c r="A6" s="5">
+        <v>3</v>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="7">
+        <v>3.000283000283e+41</v>
+      </c>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+    </row>
+    <row r="7" ht="15.15" spans="1:6">
+      <c r="A7" s="5">
+        <v>4</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="7">
+        <v>3.000283000283e+41</v>
+      </c>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+    </row>
+    <row r="8" ht="15.15" spans="1:6">
+      <c r="A8" s="5">
+        <v>5</v>
+      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="7">
+        <v>3.000283000283e+41</v>
+      </c>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+    </row>
+    <row r="9" ht="15.15" spans="1:6">
+      <c r="A9" s="5">
+        <v>6</v>
+      </c>
+      <c r="B9" s="6"/>
+      <c r="C9" s="7">
+        <v>3.000373000373e+41</v>
+      </c>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+    </row>
+    <row r="10" ht="15.15" spans="1:6">
+      <c r="A10" s="5">
+        <v>7</v>
+      </c>
+      <c r="B10" s="6"/>
+      <c r="C10" s="7">
+        <v>3.000373000373e+41</v>
+      </c>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+    </row>
+    <row r="11" ht="15.15" spans="1:6">
+      <c r="A11" s="5">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6"/>
+      <c r="C11" s="7">
+        <v>3.000283000283e+41</v>
+      </c>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+    </row>
+    <row r="12" ht="15.15" spans="1:6">
+      <c r="A12" s="5">
+        <v>9</v>
+      </c>
+      <c r="B12" s="6"/>
+      <c r="C12" s="7">
+        <v>3.000283000283e+41</v>
+      </c>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+    </row>
+    <row r="13" ht="15.15" spans="1:6">
+      <c r="A13" s="5">
+        <v>10</v>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="7">
+        <v>3.000283000283e+59</v>
+      </c>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+    </row>
+    <row r="14" ht="15.15" spans="1:6">
+      <c r="A14" s="5">
+        <v>11</v>
+      </c>
+      <c r="B14" s="6"/>
+      <c r="C14" s="7">
+        <v>3.000283000283e+59</v>
+      </c>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+    </row>
+    <row r="15" ht="15.15" spans="1:6">
+      <c r="A15" s="5">
+        <v>12</v>
+      </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="7">
+        <v>3.000283000283e+59</v>
+      </c>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+    </row>
+    <row r="16" ht="15.15" spans="1:6">
+      <c r="A16" s="5">
+        <v>13</v>
+      </c>
+      <c r="B16" s="6"/>
+      <c r="C16" s="7">
+        <v>3.000283000283e+59</v>
+      </c>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+    </row>
+    <row r="17" ht="15.15" spans="1:6">
+      <c r="A17" s="5">
+        <v>14</v>
+      </c>
+      <c r="B17" s="6"/>
+      <c r="C17" s="7">
+        <v>3.000373000373e+59</v>
+      </c>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+    </row>
+    <row r="18" ht="15.15" spans="1:6">
+      <c r="A18" s="5">
+        <v>15</v>
+      </c>
+      <c r="B18" s="6"/>
+      <c r="C18" s="7">
+        <v>3.000283000283e+59</v>
+      </c>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>